--- a/data/trans_orig/P6605-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P6605-Estudios-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según la exposición a tareas repetitivas de menos de 10 minutos /Movimientos repetitivos de manos o brazos en su trabajo en 2007</t>
+          <t>Población según la exposición a tareas repetitivas de menos de 10 minutos /Movimientos repetitivos de manos o brazos en su trabajo en 2007 (tasa de respuesta: 99,4%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>77795</t>
+          <t>79463</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>113101</t>
+          <t>113388</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>20,72%</t>
+          <t>21,16%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>30,12%</t>
+          <t>30,19%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>30096</t>
+          <t>31354</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>53784</t>
+          <t>52614</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>19,74%</t>
+          <t>20,56%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>35,28%</t>
+          <t>34,51%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>118341</t>
+          <t>117874</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>158040</t>
+          <t>156654</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>22,41%</t>
+          <t>22,33%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>29,93%</t>
+          <t>29,67%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>43177</t>
+          <t>42870</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>71585</t>
+          <t>71011</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>11,5%</t>
+          <t>11,42%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>19,06%</t>
+          <t>18,91%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>17465</t>
+          <t>18072</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>36620</t>
+          <t>37062</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>11,46%</t>
+          <t>11,85%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>24,02%</t>
+          <t>24,31%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>65447</t>
+          <t>65438</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>100181</t>
+          <t>98881</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>12,4%</t>
+          <t>12,39%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>18,97%</t>
+          <t>18,73%</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>105982</t>
+          <t>106920</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>144225</t>
+          <t>143480</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>28,22%</t>
+          <t>28,47%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>38,41%</t>
+          <t>38,21%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>27538</t>
+          <t>26963</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>49369</t>
+          <t>47501</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>18,06%</t>
+          <t>17,68%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>32,38%</t>
+          <t>31,15%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>141968</t>
+          <t>140911</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>184074</t>
+          <t>184535</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>26,89%</t>
+          <t>26,69%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>34,86%</t>
+          <t>34,95%</t>
         </is>
       </c>
     </row>
@@ -1072,12 +1072,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>83272</t>
+          <t>82106</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>117171</t>
+          <t>118121</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1087,12 +1087,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>22,18%</t>
+          <t>21,86%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>31,2%</t>
+          <t>31,46%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>35468</t>
+          <t>36312</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>58852</t>
+          <t>60269</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1122,12 +1122,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>23,26%</t>
+          <t>23,82%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>38,6%</t>
+          <t>39,53%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1142,12 +1142,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>124750</t>
+          <t>125687</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>167114</t>
+          <t>166627</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>23,63%</t>
+          <t>23,8%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>31,65%</t>
+          <t>31,56%</t>
         </is>
       </c>
     </row>
@@ -1302,12 +1302,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>238098</t>
+          <t>239050</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>296980</t>
+          <t>295037</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1317,12 +1317,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>21,22%</t>
+          <t>21,31%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>26,47%</t>
+          <t>26,3%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1337,12 +1337,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>143471</t>
+          <t>143917</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>187208</t>
+          <t>186941</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1352,12 +1352,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>24,71%</t>
+          <t>24,78%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>32,24%</t>
+          <t>32,19%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1372,12 +1372,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>397579</t>
+          <t>395336</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>470930</t>
+          <t>468521</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1387,12 +1387,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>23,35%</t>
+          <t>23,22%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>27,66%</t>
+          <t>27,52%</t>
         </is>
       </c>
     </row>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>231524</t>
+          <t>232112</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>291224</t>
+          <t>292303</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1430,12 +1430,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>20,63%</t>
+          <t>20,69%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>25,96%</t>
+          <t>26,05%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1450,12 +1450,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>114244</t>
+          <t>113509</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>155455</t>
+          <t>156147</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1465,12 +1465,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>19,67%</t>
+          <t>19,55%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>26,77%</t>
+          <t>26,89%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>359635</t>
+          <t>357079</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>429295</t>
+          <t>427447</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>21,12%</t>
+          <t>20,97%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>25,21%</t>
+          <t>25,1%</t>
         </is>
       </c>
     </row>
@@ -1528,12 +1528,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>270748</t>
+          <t>270806</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>331464</t>
+          <t>329977</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1543,12 +1543,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>24,13%</t>
+          <t>24,14%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>29,54%</t>
+          <t>29,41%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1563,12 +1563,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>140081</t>
+          <t>139677</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>184765</t>
+          <t>185865</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1578,12 +1578,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>24,12%</t>
+          <t>24,05%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>31,82%</t>
+          <t>32,01%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1598,12 +1598,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>428033</t>
+          <t>428571</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>503754</t>
+          <t>502037</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1613,12 +1613,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>25,14%</t>
+          <t>25,17%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>29,59%</t>
+          <t>29,48%</t>
         </is>
       </c>
     </row>
@@ -1641,12 +1641,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>266768</t>
+          <t>265558</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>329035</t>
+          <t>324381</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1656,12 +1656,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>23,78%</t>
+          <t>23,67%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>29,33%</t>
+          <t>28,91%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1676,12 +1676,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>101108</t>
+          <t>101541</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>140439</t>
+          <t>141213</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1691,12 +1691,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>17,41%</t>
+          <t>17,49%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>24,18%</t>
+          <t>24,32%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1711,12 +1711,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>376166</t>
+          <t>380314</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>452399</t>
+          <t>451250</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1726,12 +1726,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>22,09%</t>
+          <t>22,34%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>26,57%</t>
+          <t>26,5%</t>
         </is>
       </c>
     </row>
@@ -1871,12 +1871,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>136956</t>
+          <t>135910</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>177315</t>
+          <t>177622</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1886,12 +1886,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>33,87%</t>
+          <t>33,61%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>43,85%</t>
+          <t>43,93%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1906,12 +1906,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>94112</t>
+          <t>92832</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>126471</t>
+          <t>125651</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1921,12 +1921,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>32,43%</t>
+          <t>31,99%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>43,58%</t>
+          <t>43,3%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1941,12 +1941,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>241209</t>
+          <t>241163</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>293200</t>
+          <t>294865</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1956,12 +1956,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>34,73%</t>
+          <t>34,72%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>42,22%</t>
+          <t>42,46%</t>
         </is>
       </c>
     </row>
@@ -1984,12 +1984,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>104493</t>
+          <t>104521</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>142478</t>
+          <t>144906</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1999,12 +1999,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>25,84%</t>
+          <t>25,85%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>35,24%</t>
+          <t>35,84%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2019,12 +2019,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>69465</t>
+          <t>71104</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>103385</t>
+          <t>102207</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2034,12 +2034,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>23,94%</t>
+          <t>24,5%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>35,63%</t>
+          <t>35,22%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2054,12 +2054,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>185655</t>
+          <t>185300</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>234868</t>
+          <t>235487</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2069,12 +2069,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>26,73%</t>
+          <t>26,68%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>33,82%</t>
+          <t>33,91%</t>
         </is>
       </c>
     </row>
@@ -2097,12 +2097,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>61153</t>
+          <t>60801</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>93340</t>
+          <t>93540</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2112,12 +2112,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>15,12%</t>
+          <t>15,04%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>23,08%</t>
+          <t>23,13%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2132,12 +2132,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>60786</t>
+          <t>59641</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>91868</t>
+          <t>88546</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2147,12 +2147,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>20,95%</t>
+          <t>20,55%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>31,66%</t>
+          <t>30,51%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,12 +2167,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>128182</t>
+          <t>127653</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>173194</t>
+          <t>172361</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2182,12 +2182,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>18,46%</t>
+          <t>18,38%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>24,94%</t>
+          <t>24,82%</t>
         </is>
       </c>
     </row>
@@ -2210,12 +2210,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>36063</t>
+          <t>34975</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>62393</t>
+          <t>63264</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2225,12 +2225,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>8,92%</t>
+          <t>8,65%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>15,43%</t>
+          <t>15,65%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2245,12 +2245,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>13006</t>
+          <t>12647</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>32185</t>
+          <t>31294</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2260,12 +2260,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>4,48%</t>
+          <t>4,36%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>11,09%</t>
+          <t>10,78%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,12 +2280,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>53296</t>
+          <t>54644</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>85506</t>
+          <t>88810</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2295,12 +2295,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>7,67%</t>
+          <t>7,87%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>12,31%</t>
+          <t>12,79%</t>
         </is>
       </c>
     </row>
@@ -2440,12 +2440,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>484110</t>
+          <t>484338</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>560919</t>
+          <t>561022</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2455,12 +2455,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>25,45%</t>
+          <t>25,47%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>29,49%</t>
+          <t>29,5%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2475,12 +2475,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>287507</t>
+          <t>287696</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>347767</t>
+          <t>346778</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2490,12 +2490,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>28,09%</t>
+          <t>28,11%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>33,98%</t>
+          <t>33,89%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2510,12 +2510,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>788171</t>
+          <t>788231</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>885846</t>
+          <t>888929</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2525,12 +2525,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>26,94%</t>
+          <t>26,95%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>30,28%</t>
+          <t>30,39%</t>
         </is>
       </c>
     </row>
@@ -2553,12 +2553,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>398633</t>
+          <t>400897</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>472109</t>
+          <t>475390</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2568,12 +2568,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>20,96%</t>
+          <t>21,08%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>24,82%</t>
+          <t>25,0%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2588,12 +2588,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>220243</t>
+          <t>218532</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>272530</t>
+          <t>275727</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2603,12 +2603,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>21,52%</t>
+          <t>21,35%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>26,63%</t>
+          <t>26,94%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2623,12 +2623,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>640525</t>
+          <t>637632</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>730071</t>
+          <t>734217</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2638,12 +2638,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>21,9%</t>
+          <t>21,8%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>24,96%</t>
+          <t>25,1%</t>
         </is>
       </c>
     </row>
@@ -2666,12 +2666,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>461681</t>
+          <t>465505</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>541155</t>
+          <t>541781</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2681,12 +2681,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>24,27%</t>
+          <t>24,48%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>28,45%</t>
+          <t>28,49%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2701,12 +2701,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>245797</t>
+          <t>245867</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>302929</t>
+          <t>300873</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2716,12 +2716,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>24,02%</t>
+          <t>24,03%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>29,6%</t>
+          <t>29,4%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2736,12 +2736,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>724906</t>
+          <t>724939</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>824331</t>
+          <t>825722</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2756,7 +2756,7 @@
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>28,18%</t>
+          <t>28,23%</t>
         </is>
       </c>
     </row>
@@ -2779,12 +2779,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>406995</t>
+          <t>408239</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>481146</t>
+          <t>480945</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2794,12 +2794,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>21,4%</t>
+          <t>21,47%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>25,3%</t>
+          <t>25,29%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2814,12 +2814,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>163918</t>
+          <t>162162</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>212985</t>
+          <t>212380</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2829,12 +2829,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>16,02%</t>
+          <t>15,85%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>20,81%</t>
+          <t>20,75%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2849,12 +2849,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>584254</t>
+          <t>584980</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>675328</t>
+          <t>676047</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2864,12 +2864,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>19,97%</t>
+          <t>20,0%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>23,09%</t>
+          <t>23,11%</t>
         </is>
       </c>
     </row>
@@ -3045,7 +3045,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según la exposición a tareas repetitivas de menos de 10 minutos /Movimientos repetitivos de manos o brazos en su trabajo en 2012</t>
+          <t>Población según la exposición a tareas repetitivas de menos de 10 minutos /Movimientos repetitivos de manos o brazos en su trabajo en 2012 (tasa de respuesta: 99,14%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3240,12 +3240,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>17163</t>
+          <t>17440</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>37165</t>
+          <t>37773</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3255,12 +3255,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>9,43%</t>
+          <t>9,59%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>20,43%</t>
+          <t>20,77%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3275,12 +3275,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>22197</t>
+          <t>22164</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>43568</t>
+          <t>44314</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3290,12 +3290,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>15,86%</t>
+          <t>15,83%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>31,13%</t>
+          <t>31,66%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3310,12 +3310,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>45518</t>
+          <t>46092</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>72925</t>
+          <t>74482</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3325,12 +3325,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>14,14%</t>
+          <t>14,32%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>22,66%</t>
+          <t>23,14%</t>
         </is>
       </c>
     </row>
@@ -3353,12 +3353,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>27898</t>
+          <t>26993</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>50664</t>
+          <t>49495</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3368,12 +3368,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>15,34%</t>
+          <t>14,84%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>27,85%</t>
+          <t>27,21%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3388,12 +3388,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>32673</t>
+          <t>32134</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>54893</t>
+          <t>54414</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3403,12 +3403,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>23,34%</t>
+          <t>22,96%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>39,22%</t>
+          <t>38,87%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3423,12 +3423,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>66401</t>
+          <t>65732</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>98690</t>
+          <t>97677</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3438,12 +3438,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>20,63%</t>
+          <t>20,42%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>30,66%</t>
+          <t>30,35%</t>
         </is>
       </c>
     </row>
@@ -3466,12 +3466,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>56838</t>
+          <t>57460</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>83409</t>
+          <t>85674</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3481,12 +3481,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>31,25%</t>
+          <t>31,59%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>45,85%</t>
+          <t>47,1%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -3501,12 +3501,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>15417</t>
+          <t>15251</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>32626</t>
+          <t>33104</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3516,12 +3516,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>11,01%</t>
+          <t>10,9%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>23,31%</t>
+          <t>23,65%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3536,12 +3536,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>77645</t>
+          <t>77509</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>110788</t>
+          <t>109922</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -3551,12 +3551,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>24,12%</t>
+          <t>24,08%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>34,42%</t>
+          <t>34,15%</t>
         </is>
       </c>
     </row>
@@ -3579,12 +3579,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>35936</t>
+          <t>36808</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>61300</t>
+          <t>61833</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3594,12 +3594,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>19,76%</t>
+          <t>20,23%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>33,7%</t>
+          <t>33,99%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3614,12 +3614,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>31125</t>
+          <t>31344</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>53574</t>
+          <t>52784</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3629,12 +3629,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>22,24%</t>
+          <t>22,39%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>38,27%</t>
+          <t>37,71%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3649,12 +3649,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>73541</t>
+          <t>73347</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>106798</t>
+          <t>106844</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3664,12 +3664,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>22,85%</t>
+          <t>22,79%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>33,18%</t>
+          <t>33,19%</t>
         </is>
       </c>
     </row>
@@ -3809,12 +3809,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>162936</t>
+          <t>161525</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>213913</t>
+          <t>212334</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -3824,12 +3824,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>17,87%</t>
+          <t>17,71%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>23,46%</t>
+          <t>23,29%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -3844,12 +3844,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>116946</t>
+          <t>115133</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>157456</t>
+          <t>156616</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3859,12 +3859,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>20,45%</t>
+          <t>20,13%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>27,53%</t>
+          <t>27,39%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -3879,12 +3879,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>290866</t>
+          <t>291456</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>356815</t>
+          <t>360301</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -3894,12 +3894,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>19,6%</t>
+          <t>19,64%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>24,05%</t>
+          <t>24,28%</t>
         </is>
       </c>
     </row>
@@ -3922,12 +3922,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>212792</t>
+          <t>211009</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>267672</t>
+          <t>266136</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3937,12 +3937,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>23,34%</t>
+          <t>23,14%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>29,36%</t>
+          <t>29,19%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3957,12 +3957,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>117469</t>
+          <t>117293</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>158626</t>
+          <t>157107</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3972,12 +3972,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>20,54%</t>
+          <t>20,51%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>27,74%</t>
+          <t>27,47%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3992,12 +3992,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>344628</t>
+          <t>341888</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>413017</t>
+          <t>412270</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4007,12 +4007,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>23,23%</t>
+          <t>23,04%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>27,84%</t>
+          <t>27,79%</t>
         </is>
       </c>
     </row>
@@ -4035,12 +4035,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>239744</t>
+          <t>237966</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>297041</t>
+          <t>296447</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4050,12 +4050,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>26,29%</t>
+          <t>26,1%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>32,58%</t>
+          <t>32,51%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4070,12 +4070,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>135324</t>
+          <t>135907</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>177629</t>
+          <t>180513</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4085,12 +4085,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>23,66%</t>
+          <t>23,77%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>31,06%</t>
+          <t>31,57%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4105,12 +4105,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>389194</t>
+          <t>385463</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>461554</t>
+          <t>461633</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4120,7 +4120,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>26,23%</t>
+          <t>25,98%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -4148,12 +4148,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>190694</t>
+          <t>190042</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>244269</t>
+          <t>244554</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -4163,12 +4163,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>20,91%</t>
+          <t>20,84%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>26,79%</t>
+          <t>26,82%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -4183,12 +4183,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>121374</t>
+          <t>121873</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>164388</t>
+          <t>165762</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4198,12 +4198,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>21,22%</t>
+          <t>21,31%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>28,75%</t>
+          <t>28,99%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -4218,12 +4218,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>327347</t>
+          <t>323477</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>394588</t>
+          <t>392515</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4233,12 +4233,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>22,06%</t>
+          <t>21,8%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>26,59%</t>
+          <t>26,46%</t>
         </is>
       </c>
     </row>
@@ -4378,12 +4378,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>92905</t>
+          <t>95261</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>129943</t>
+          <t>130845</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4393,12 +4393,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>29,38%</t>
+          <t>30,12%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>41,09%</t>
+          <t>41,37%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4413,12 +4413,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>66930</t>
+          <t>67161</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>99287</t>
+          <t>97229</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4428,12 +4428,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>28,49%</t>
+          <t>28,59%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>42,27%</t>
+          <t>41,39%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4448,12 +4448,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>172272</t>
+          <t>169456</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>218249</t>
+          <t>217946</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4463,12 +4463,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>31,26%</t>
+          <t>30,75%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>39,6%</t>
+          <t>39,54%</t>
         </is>
       </c>
     </row>
@@ -4491,12 +4491,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>57156</t>
+          <t>54900</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>88915</t>
+          <t>87029</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>18,07%</t>
+          <t>17,36%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>28,11%</t>
+          <t>27,52%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -4526,12 +4526,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>59542</t>
+          <t>58732</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>89696</t>
+          <t>89325</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -4541,12 +4541,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>25,35%</t>
+          <t>25,0%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>38,19%</t>
+          <t>38,03%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -4561,12 +4561,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>122978</t>
+          <t>121075</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>166462</t>
+          <t>166787</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -4576,12 +4576,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>22,31%</t>
+          <t>21,97%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>30,2%</t>
+          <t>30,26%</t>
         </is>
       </c>
     </row>
@@ -4604,12 +4604,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>68561</t>
+          <t>68442</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>102043</t>
+          <t>102914</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4619,12 +4619,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>21,68%</t>
+          <t>21,64%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>32,27%</t>
+          <t>32,54%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4639,12 +4639,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>40264</t>
+          <t>42206</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>69104</t>
+          <t>69112</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4654,7 +4654,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>17,14%</t>
+          <t>17,97%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -4674,12 +4674,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>118532</t>
+          <t>115727</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>163242</t>
+          <t>161807</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4689,12 +4689,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>21,51%</t>
+          <t>21,0%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>29,62%</t>
+          <t>29,36%</t>
         </is>
       </c>
     </row>
@@ -4717,12 +4717,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>35893</t>
+          <t>37232</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>64277</t>
+          <t>64642</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4732,12 +4732,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>11,35%</t>
+          <t>11,77%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>20,32%</t>
+          <t>20,44%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4752,12 +4752,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>17520</t>
+          <t>17429</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>38481</t>
+          <t>37221</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4767,12 +4767,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>7,46%</t>
+          <t>7,42%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>16,38%</t>
+          <t>15,85%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4787,12 +4787,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>60361</t>
+          <t>59177</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>94726</t>
+          <t>94194</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4802,12 +4802,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>10,95%</t>
+          <t>10,74%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>17,19%</t>
+          <t>17,09%</t>
         </is>
       </c>
     </row>
@@ -4947,12 +4947,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>293127</t>
+          <t>293884</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>357959</t>
+          <t>359510</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -4962,12 +4962,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>20,79%</t>
+          <t>20,84%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>25,39%</t>
+          <t>25,5%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -4982,12 +4982,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>219618</t>
+          <t>222884</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>276758</t>
+          <t>277835</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -4997,12 +4997,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>23,2%</t>
+          <t>23,54%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>29,23%</t>
+          <t>29,35%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5017,12 +5017,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>532098</t>
+          <t>529478</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>620875</t>
+          <t>618960</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5032,12 +5032,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>22,58%</t>
+          <t>22,47%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>26,34%</t>
+          <t>26,26%</t>
         </is>
       </c>
     </row>
@@ -5060,12 +5060,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>313849</t>
+          <t>314485</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>383637</t>
+          <t>379593</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5075,12 +5075,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>22,26%</t>
+          <t>22,3%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>27,21%</t>
+          <t>26,92%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5095,12 +5095,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>225443</t>
+          <t>224750</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>280878</t>
+          <t>281818</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5110,12 +5110,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>23,81%</t>
+          <t>23,74%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>29,67%</t>
+          <t>29,77%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5130,12 +5130,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>559575</t>
+          <t>562081</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>644350</t>
+          <t>651677</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5145,12 +5145,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>23,74%</t>
+          <t>23,85%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>27,34%</t>
+          <t>27,65%</t>
         </is>
       </c>
     </row>
@@ -5173,12 +5173,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>388203</t>
+          <t>387210</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>457847</t>
+          <t>456238</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -5188,12 +5188,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>27,53%</t>
+          <t>27,46%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>32,47%</t>
+          <t>32,36%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -5208,12 +5208,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>208190</t>
+          <t>207412</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>263032</t>
+          <t>264249</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -5223,12 +5223,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>21,99%</t>
+          <t>21,91%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>27,78%</t>
+          <t>27,91%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -5243,12 +5243,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>607437</t>
+          <t>612533</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>698484</t>
+          <t>701561</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -5258,12 +5258,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>25,77%</t>
+          <t>25,99%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>29,64%</t>
+          <t>29,77%</t>
         </is>
       </c>
     </row>
@@ -5286,12 +5286,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>282867</t>
+          <t>281556</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>350495</t>
+          <t>344706</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5301,12 +5301,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>20,06%</t>
+          <t>19,97%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>24,86%</t>
+          <t>24,45%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5321,12 +5321,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>185101</t>
+          <t>183609</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>239320</t>
+          <t>236719</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5336,12 +5336,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>19,55%</t>
+          <t>19,39%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>25,28%</t>
+          <t>25,0%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5356,12 +5356,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>480859</t>
+          <t>478292</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>565912</t>
+          <t>566602</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5371,12 +5371,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>20,4%</t>
+          <t>20,29%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>24,01%</t>
+          <t>24,04%</t>
         </is>
       </c>
     </row>
@@ -5552,7 +5552,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según la exposición a tareas repetitivas de menos de 10 minutos /Movimientos repetitivos de manos o brazos en su trabajo en 2016</t>
+          <t>Población según la exposición a tareas repetitivas de menos de 10 minutos /Movimientos repetitivos de manos o brazos en su trabajo en 2016 (tasa de respuesta: 99,49%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -5747,12 +5747,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>12533</t>
+          <t>12907</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>29528</t>
+          <t>28994</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5762,12 +5762,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>9,03%</t>
+          <t>9,29%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>21,26%</t>
+          <t>20,88%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5782,12 +5782,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>9868</t>
+          <t>9961</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>24030</t>
+          <t>23309</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5797,12 +5797,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>13,69%</t>
+          <t>13,82%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>33,34%</t>
+          <t>32,34%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5817,12 +5817,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>25381</t>
+          <t>25536</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>47692</t>
+          <t>47055</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5832,12 +5832,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>12,03%</t>
+          <t>12,11%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>22,61%</t>
+          <t>22,31%</t>
         </is>
       </c>
     </row>
@@ -5860,12 +5860,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>24187</t>
+          <t>23958</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>44422</t>
+          <t>44858</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5875,12 +5875,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>17,42%</t>
+          <t>17,25%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>31,99%</t>
+          <t>32,3%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5895,12 +5895,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>12144</t>
+          <t>12447</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>26556</t>
+          <t>26456</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5910,12 +5910,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>16,85%</t>
+          <t>17,27%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>36,84%</t>
+          <t>36,7%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5930,12 +5930,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>41175</t>
+          <t>41320</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>66441</t>
+          <t>65814</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5945,12 +5945,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>19,52%</t>
+          <t>19,59%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>31,5%</t>
+          <t>31,2%</t>
         </is>
       </c>
     </row>
@@ -5973,12 +5973,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>33433</t>
+          <t>34165</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>55737</t>
+          <t>55863</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5988,12 +5988,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>24,08%</t>
+          <t>24,6%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>40,14%</t>
+          <t>40,23%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -6008,12 +6008,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>11001</t>
+          <t>11342</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>25802</t>
+          <t>26094</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6023,47 +6023,47 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>15,26%</t>
+          <t>15,73%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
+          <t>36,2%</t>
+        </is>
+      </c>
+      <c r="Q6" s="2" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="R6" s="2" t="inlineStr">
+        <is>
+          <t>61484</t>
+        </is>
+      </c>
+      <c r="S6" s="2" t="inlineStr">
+        <is>
+          <t>49500</t>
+        </is>
+      </c>
+      <c r="T6" s="2" t="inlineStr">
+        <is>
+          <t>75507</t>
+        </is>
+      </c>
+      <c r="U6" s="2" t="inlineStr">
+        <is>
+          <t>29,15%</t>
+        </is>
+      </c>
+      <c r="V6" s="2" t="inlineStr">
+        <is>
+          <t>23,47%</t>
+        </is>
+      </c>
+      <c r="W6" s="2" t="inlineStr">
+        <is>
           <t>35,79%</t>
-        </is>
-      </c>
-      <c r="Q6" s="2" t="inlineStr">
-        <is>
-          <t>61</t>
-        </is>
-      </c>
-      <c r="R6" s="2" t="inlineStr">
-        <is>
-          <t>61484</t>
-        </is>
-      </c>
-      <c r="S6" s="2" t="inlineStr">
-        <is>
-          <t>48632</t>
-        </is>
-      </c>
-      <c r="T6" s="2" t="inlineStr">
-        <is>
-          <t>74742</t>
-        </is>
-      </c>
-      <c r="U6" s="2" t="inlineStr">
-        <is>
-          <t>29,15%</t>
-        </is>
-      </c>
-      <c r="V6" s="2" t="inlineStr">
-        <is>
-          <t>23,05%</t>
-        </is>
-      </c>
-      <c r="W6" s="2" t="inlineStr">
-        <is>
-          <t>35,43%</t>
         </is>
       </c>
     </row>
@@ -6086,12 +6086,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>30662</t>
+          <t>31111</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>52372</t>
+          <t>53980</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6101,12 +6101,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>22,08%</t>
+          <t>22,4%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>37,72%</t>
+          <t>38,87%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6121,12 +6121,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>13008</t>
+          <t>13229</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>28135</t>
+          <t>27637</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6136,12 +6136,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>18,05%</t>
+          <t>18,35%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>39,03%</t>
+          <t>38,34%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6156,12 +6156,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>47597</t>
+          <t>48758</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>75785</t>
+          <t>75423</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6171,12 +6171,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>22,56%</t>
+          <t>23,11%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>35,93%</t>
+          <t>35,75%</t>
         </is>
       </c>
     </row>
@@ -6316,12 +6316,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>204343</t>
+          <t>205493</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>258285</t>
+          <t>261195</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -6331,12 +6331,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>22,18%</t>
+          <t>22,3%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>28,03%</t>
+          <t>28,34%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -6351,12 +6351,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>170892</t>
+          <t>170084</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>217573</t>
+          <t>215458</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -6366,12 +6366,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>26,26%</t>
+          <t>26,13%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>33,43%</t>
+          <t>33,11%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -6386,12 +6386,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>388945</t>
+          <t>389324</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>460614</t>
+          <t>457557</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -6401,12 +6401,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>24,74%</t>
+          <t>24,76%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>29,3%</t>
+          <t>29,1%</t>
         </is>
       </c>
     </row>
@@ -6429,12 +6429,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>200673</t>
+          <t>200095</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>252173</t>
+          <t>256261</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6444,12 +6444,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>21,78%</t>
+          <t>21,71%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>27,37%</t>
+          <t>27,81%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6464,12 +6464,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>153439</t>
+          <t>151756</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>199598</t>
+          <t>196561</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6479,12 +6479,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>23,58%</t>
+          <t>23,32%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>30,67%</t>
+          <t>30,2%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6499,12 +6499,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>364681</t>
+          <t>365503</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>436550</t>
+          <t>435841</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6514,12 +6514,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>23,19%</t>
+          <t>23,25%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>27,77%</t>
+          <t>27,72%</t>
         </is>
       </c>
     </row>
@@ -6542,12 +6542,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>248161</t>
+          <t>250646</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>305763</t>
+          <t>308536</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6557,12 +6557,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>26,93%</t>
+          <t>27,2%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>33,18%</t>
+          <t>33,48%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6577,12 +6577,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>125377</t>
+          <t>126759</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>170330</t>
+          <t>168759</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6592,12 +6592,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>19,27%</t>
+          <t>19,48%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>26,17%</t>
+          <t>25,93%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6612,12 +6612,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>390851</t>
+          <t>393584</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>464404</t>
+          <t>465778</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6627,12 +6627,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>24,86%</t>
+          <t>25,03%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>29,54%</t>
+          <t>29,62%</t>
         </is>
       </c>
     </row>
@@ -6655,12 +6655,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>162596</t>
+          <t>161080</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>213921</t>
+          <t>213609</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -6670,12 +6670,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>17,64%</t>
+          <t>17,48%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>23,21%</t>
+          <t>23,18%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -6690,12 +6690,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>116162</t>
+          <t>115353</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>157831</t>
+          <t>157383</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6705,12 +6705,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>17,85%</t>
+          <t>17,72%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>24,25%</t>
+          <t>24,18%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -6725,12 +6725,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>290339</t>
+          <t>288072</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>355332</t>
+          <t>354940</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6740,12 +6740,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>18,47%</t>
+          <t>18,32%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>22,6%</t>
+          <t>22,57%</t>
         </is>
       </c>
     </row>
@@ -6885,12 +6885,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>140949</t>
+          <t>141758</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>179600</t>
+          <t>180956</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6900,12 +6900,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>40,42%</t>
+          <t>40,65%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>51,51%</t>
+          <t>51,89%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6920,12 +6920,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>113061</t>
+          <t>113167</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>144878</t>
+          <t>146263</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6935,12 +6935,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>36,77%</t>
+          <t>36,81%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>47,12%</t>
+          <t>47,57%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6955,12 +6955,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>263214</t>
+          <t>261620</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>316908</t>
+          <t>313298</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6970,12 +6970,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>40,11%</t>
+          <t>39,87%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>48,3%</t>
+          <t>47,75%</t>
         </is>
       </c>
     </row>
@@ -6998,12 +6998,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>72141</t>
+          <t>70482</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>106716</t>
+          <t>104244</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -7013,12 +7013,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>20,69%</t>
+          <t>20,21%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>30,6%</t>
+          <t>29,89%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -7033,12 +7033,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>54364</t>
+          <t>52253</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>82937</t>
+          <t>82228</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -7048,12 +7048,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>17,68%</t>
+          <t>17,0%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>26,98%</t>
+          <t>26,75%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -7068,12 +7068,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>131288</t>
+          <t>134176</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>175399</t>
+          <t>178326</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -7083,12 +7083,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>20,01%</t>
+          <t>20,45%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>26,73%</t>
+          <t>27,18%</t>
         </is>
       </c>
     </row>
@@ -7111,12 +7111,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>46081</t>
+          <t>46218</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>74654</t>
+          <t>74980</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7126,12 +7126,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>13,21%</t>
+          <t>13,25%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>21,41%</t>
+          <t>21,5%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7146,12 +7146,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>49694</t>
+          <t>49639</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>76403</t>
+          <t>75378</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7161,12 +7161,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>16,16%</t>
+          <t>16,15%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>24,85%</t>
+          <t>24,52%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7181,12 +7181,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>102079</t>
+          <t>102136</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>141889</t>
+          <t>141625</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7196,12 +7196,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>15,56%</t>
+          <t>15,57%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>21,62%</t>
+          <t>21,58%</t>
         </is>
       </c>
     </row>
@@ -7224,12 +7224,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>30701</t>
+          <t>30257</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>55320</t>
+          <t>55932</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7239,12 +7239,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>8,8%</t>
+          <t>8,68%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>15,86%</t>
+          <t>16,04%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7259,12 +7259,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>38747</t>
+          <t>38010</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>65033</t>
+          <t>64230</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7274,12 +7274,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>12,6%</t>
+          <t>12,36%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>21,15%</t>
+          <t>20,89%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7294,12 +7294,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>74765</t>
+          <t>74864</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>111469</t>
+          <t>111490</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7309,7 +7309,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>11,39%</t>
+          <t>11,41%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -7454,12 +7454,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>376309</t>
+          <t>376093</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>444467</t>
+          <t>447512</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -7469,12 +7469,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>26,71%</t>
+          <t>26,69%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>31,54%</t>
+          <t>31,76%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7489,12 +7489,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>309770</t>
+          <t>308561</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>371122</t>
+          <t>369517</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7504,12 +7504,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>30,07%</t>
+          <t>29,95%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>36,02%</t>
+          <t>35,86%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7524,12 +7524,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>700702</t>
+          <t>704975</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>793446</t>
+          <t>793587</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7539,7 +7539,7 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>28,72%</t>
+          <t>28,9%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
@@ -7567,12 +7567,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>317882</t>
+          <t>316966</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>383788</t>
+          <t>384727</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7582,12 +7582,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>22,56%</t>
+          <t>22,49%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>27,24%</t>
+          <t>27,3%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7602,12 +7602,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>233559</t>
+          <t>232180</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>288887</t>
+          <t>287029</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7617,12 +7617,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>22,67%</t>
+          <t>22,53%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>28,04%</t>
+          <t>27,86%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7637,12 +7637,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>566576</t>
+          <t>562986</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>654951</t>
+          <t>649322</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7652,12 +7652,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>23,23%</t>
+          <t>23,08%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>26,85%</t>
+          <t>26,62%</t>
         </is>
       </c>
     </row>
@@ -7680,12 +7680,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>348197</t>
+          <t>346452</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>417396</t>
+          <t>413524</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -7695,12 +7695,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>24,71%</t>
+          <t>24,59%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>29,62%</t>
+          <t>29,35%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -7715,12 +7715,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>200760</t>
+          <t>200573</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>253498</t>
+          <t>251980</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -7730,12 +7730,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>19,48%</t>
+          <t>19,47%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>24,6%</t>
+          <t>24,46%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -7750,12 +7750,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>567327</t>
+          <t>565806</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>653130</t>
+          <t>653356</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -7765,12 +7765,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>23,26%</t>
+          <t>23,19%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>26,77%</t>
+          <t>26,78%</t>
         </is>
       </c>
     </row>
@@ -7793,12 +7793,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>238797</t>
+          <t>240356</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>298389</t>
+          <t>302036</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -7808,12 +7808,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>16,95%</t>
+          <t>17,06%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>21,18%</t>
+          <t>21,44%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -7828,12 +7828,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>180431</t>
+          <t>178451</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>229472</t>
+          <t>230889</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -7843,12 +7843,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>17,51%</t>
+          <t>17,32%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>22,27%</t>
+          <t>22,41%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -7863,12 +7863,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>435946</t>
+          <t>438985</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>516518</t>
+          <t>515423</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -7878,12 +7878,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>17,87%</t>
+          <t>18,0%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>21,17%</t>
+          <t>21,13%</t>
         </is>
       </c>
     </row>
@@ -8059,7 +8059,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según la exposición a tareas repetitivas de menos de 10 minutos /Movimientos repetitivos de manos o brazos en su trabajo en 2023</t>
+          <t>Población según la exposición a tareas repetitivas de menos de 10 minutos /Movimientos repetitivos de manos o brazos en su trabajo en 2023 (tasa de respuesta: 99,72%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -8254,12 +8254,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>6722</t>
+          <t>7067</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>21067</t>
+          <t>21359</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -8269,12 +8269,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>10,28%</t>
+          <t>10,8%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>32,21%</t>
+          <t>32,65%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8289,12 +8289,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1468</t>
+          <t>1472</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>7444</t>
+          <t>7685</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -8304,12 +8304,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>3,75%</t>
+          <t>3,76%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>19,03%</t>
+          <t>19,64%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8324,12 +8324,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>9639</t>
+          <t>9325</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>24186</t>
+          <t>25231</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -8339,12 +8339,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>9,22%</t>
+          <t>8,92%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>23,14%</t>
+          <t>24,14%</t>
         </is>
       </c>
     </row>
@@ -8367,12 +8367,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>3996</t>
+          <t>4030</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>15134</t>
+          <t>14863</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -8382,12 +8382,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>6,11%</t>
+          <t>6,16%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>23,14%</t>
+          <t>22,72%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8402,12 +8402,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>9340</t>
+          <t>8986</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>18690</t>
+          <t>18407</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -8417,12 +8417,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>23,87%</t>
+          <t>22,97%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>47,77%</t>
+          <t>47,05%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8437,12 +8437,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>15299</t>
+          <t>15761</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>30025</t>
+          <t>30646</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -8452,12 +8452,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>14,63%</t>
+          <t>15,08%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>28,72%</t>
+          <t>29,32%</t>
         </is>
       </c>
     </row>
@@ -8480,12 +8480,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>18482</t>
+          <t>17868</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>35207</t>
+          <t>35550</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -8495,12 +8495,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>28,25%</t>
+          <t>27,32%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>53,82%</t>
+          <t>54,35%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -8515,12 +8515,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>7643</t>
+          <t>7801</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>16653</t>
+          <t>17285</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -8530,12 +8530,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>19,54%</t>
+          <t>19,94%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>42,57%</t>
+          <t>44,18%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -8550,12 +8550,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>29792</t>
+          <t>28942</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>47919</t>
+          <t>48411</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -8565,12 +8565,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>28,5%</t>
+          <t>27,69%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>45,84%</t>
+          <t>46,31%</t>
         </is>
       </c>
     </row>
@@ -8593,12 +8593,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>11583</t>
+          <t>11749</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>25939</t>
+          <t>26167</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -8608,12 +8608,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>17,71%</t>
+          <t>17,96%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>39,65%</t>
+          <t>40,0%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -8628,12 +8628,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>5752</t>
+          <t>5554</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>15330</t>
+          <t>14954</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>14,7%</t>
+          <t>14,2%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>39,18%</t>
+          <t>38,22%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -8663,12 +8663,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>20440</t>
+          <t>20206</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>36977</t>
+          <t>38224</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -8678,12 +8678,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>19,55%</t>
+          <t>19,33%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>35,37%</t>
+          <t>36,57%</t>
         </is>
       </c>
     </row>
@@ -8823,12 +8823,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>132226</t>
+          <t>134501</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>600325</t>
+          <t>611633</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -8838,12 +8838,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>16,44%</t>
+          <t>16,73%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>74,65%</t>
+          <t>76,06%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -8858,12 +8858,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>69140</t>
+          <t>68871</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>110179</t>
+          <t>110224</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -8873,12 +8873,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>15,65%</t>
+          <t>15,59%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>24,94%</t>
+          <t>24,95%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -8893,12 +8893,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>224421</t>
+          <t>223618</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>774382</t>
+          <t>826867</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -8908,12 +8908,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>18,01%</t>
+          <t>17,95%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>62,15%</t>
+          <t>66,36%</t>
         </is>
       </c>
     </row>
@@ -8936,12 +8936,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>77454</t>
+          <t>72920</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>259243</t>
+          <t>261003</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8951,12 +8951,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>9,63%</t>
+          <t>9,07%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>32,24%</t>
+          <t>32,46%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8971,12 +8971,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>97478</t>
+          <t>98611</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>147746</t>
+          <t>146292</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8986,12 +8986,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>22,07%</t>
+          <t>22,32%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>33,45%</t>
+          <t>33,12%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -9006,12 +9006,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>171587</t>
+          <t>153430</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>384740</t>
+          <t>389598</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -9021,12 +9021,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>13,77%</t>
+          <t>12,31%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>30,88%</t>
+          <t>31,27%</t>
         </is>
       </c>
     </row>
@@ -9049,12 +9049,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>83310</t>
+          <t>81763</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>299333</t>
+          <t>300892</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -9064,12 +9064,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>10,36%</t>
+          <t>10,17%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>37,22%</t>
+          <t>37,42%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -9084,12 +9084,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>88848</t>
+          <t>88047</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>133564</t>
+          <t>131871</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -9099,12 +9099,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>20,11%</t>
+          <t>19,93%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>30,23%</t>
+          <t>29,85%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -9119,12 +9119,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>176407</t>
+          <t>151401</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>408006</t>
+          <t>407290</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -9134,12 +9134,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>14,16%</t>
+          <t>12,15%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>32,75%</t>
+          <t>32,69%</t>
         </is>
       </c>
     </row>
@@ -9162,12 +9162,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>36313</t>
+          <t>35129</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>135506</t>
+          <t>132229</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -9177,12 +9177,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>4,52%</t>
+          <t>4,37%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>16,85%</t>
+          <t>16,44%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -9197,12 +9197,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>76534</t>
+          <t>78636</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>186165</t>
+          <t>184383</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -9212,12 +9212,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>17,32%</t>
+          <t>17,8%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>42,14%</t>
+          <t>41,74%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -9232,12 +9232,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>103679</t>
+          <t>110685</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>286916</t>
+          <t>284162</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -9247,12 +9247,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>8,32%</t>
+          <t>8,88%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>23,03%</t>
+          <t>22,81%</t>
         </is>
       </c>
     </row>
@@ -9392,12 +9392,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>114982</t>
+          <t>113711</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>147293</t>
+          <t>146043</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -9407,12 +9407,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>47,5%</t>
+          <t>46,98%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>60,85%</t>
+          <t>60,33%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9427,12 +9427,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>79776</t>
+          <t>79232</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>103342</t>
+          <t>104240</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -9442,12 +9442,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>40,08%</t>
+          <t>39,8%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>51,91%</t>
+          <t>52,36%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9462,12 +9462,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>201153</t>
+          <t>202345</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>245086</t>
+          <t>242722</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -9477,12 +9477,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>45,6%</t>
+          <t>45,87%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>55,56%</t>
+          <t>55,02%</t>
         </is>
       </c>
     </row>
@@ -9505,12 +9505,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>40142</t>
+          <t>39923</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>67078</t>
+          <t>66626</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -9520,12 +9520,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>16,58%</t>
+          <t>16,49%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>27,71%</t>
+          <t>27,52%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -9540,12 +9540,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>45840</t>
+          <t>44828</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>66526</t>
+          <t>65792</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -9555,12 +9555,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>23,03%</t>
+          <t>22,52%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>33,42%</t>
+          <t>33,05%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -9575,12 +9575,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>91426</t>
+          <t>91652</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>126336</t>
+          <t>125478</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -9590,12 +9590,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>20,73%</t>
+          <t>20,78%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>28,64%</t>
+          <t>28,45%</t>
         </is>
       </c>
     </row>
@@ -9618,12 +9618,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>27006</t>
+          <t>27501</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>51488</t>
+          <t>51181</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -9633,12 +9633,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>11,16%</t>
+          <t>11,36%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>21,27%</t>
+          <t>21,14%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -9653,12 +9653,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>22966</t>
+          <t>22697</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>41473</t>
+          <t>42384</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -9668,12 +9668,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>11,54%</t>
+          <t>11,4%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>20,83%</t>
+          <t>21,29%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -9688,12 +9688,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>54259</t>
+          <t>55470</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>84077</t>
+          <t>84896</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -9703,12 +9703,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>12,3%</t>
+          <t>12,57%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>19,06%</t>
+          <t>19,25%</t>
         </is>
       </c>
     </row>
@@ -9731,12 +9731,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>11705</t>
+          <t>11095</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>35147</t>
+          <t>34394</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -9746,12 +9746,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>4,84%</t>
+          <t>4,58%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>14,52%</t>
+          <t>14,21%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -9766,12 +9766,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>13485</t>
+          <t>13853</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>31577</t>
+          <t>30679</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -9781,47 +9781,47 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
+          <t>6,96%</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr">
+        <is>
+          <t>15,41%</t>
+        </is>
+      </c>
+      <c r="Q17" s="2" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="R17" s="2" t="inlineStr">
+        <is>
+          <t>41071</t>
+        </is>
+      </c>
+      <c r="S17" s="2" t="inlineStr">
+        <is>
+          <t>29848</t>
+        </is>
+      </c>
+      <c r="T17" s="2" t="inlineStr">
+        <is>
+          <t>57771</t>
+        </is>
+      </c>
+      <c r="U17" s="2" t="inlineStr">
+        <is>
+          <t>9,31%</t>
+        </is>
+      </c>
+      <c r="V17" s="2" t="inlineStr">
+        <is>
           <t>6,77%</t>
         </is>
       </c>
-      <c r="P17" s="2" t="inlineStr">
-        <is>
-          <t>15,86%</t>
-        </is>
-      </c>
-      <c r="Q17" s="2" t="inlineStr">
-        <is>
-          <t>41</t>
-        </is>
-      </c>
-      <c r="R17" s="2" t="inlineStr">
-        <is>
-          <t>41071</t>
-        </is>
-      </c>
-      <c r="S17" s="2" t="inlineStr">
-        <is>
-          <t>29928</t>
-        </is>
-      </c>
-      <c r="T17" s="2" t="inlineStr">
-        <is>
-          <t>55975</t>
-        </is>
-      </c>
-      <c r="U17" s="2" t="inlineStr">
-        <is>
-          <t>9,31%</t>
-        </is>
-      </c>
-      <c r="V17" s="2" t="inlineStr">
-        <is>
-          <t>6,78%</t>
-        </is>
-      </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>12,69%</t>
+          <t>13,1%</t>
         </is>
       </c>
     </row>
@@ -9961,12 +9961,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>303476</t>
+          <t>301580</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>789744</t>
+          <t>754875</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9976,12 +9976,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>27,3%</t>
+          <t>27,13%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>71,04%</t>
+          <t>67,91%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9996,12 +9996,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>158549</t>
+          <t>154409</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>209763</t>
+          <t>208309</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -10011,12 +10011,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>23,32%</t>
+          <t>22,71%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>30,85%</t>
+          <t>30,64%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -10031,12 +10031,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>483281</t>
+          <t>477892</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>1048730</t>
+          <t>1086206</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -10046,12 +10046,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>26,97%</t>
+          <t>26,67%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>58,54%</t>
+          <t>60,63%</t>
         </is>
       </c>
     </row>
@@ -10074,12 +10074,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>121812</t>
+          <t>129714</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>313016</t>
+          <t>312963</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -10089,12 +10089,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>10,96%</t>
+          <t>11,67%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>28,16%</t>
+          <t>28,15%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -10109,12 +10109,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>164554</t>
+          <t>164478</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>219081</t>
+          <t>218446</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -10124,12 +10124,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>24,2%</t>
+          <t>24,19%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>32,22%</t>
+          <t>32,13%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -10144,12 +10144,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>281218</t>
+          <t>268649</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>517330</t>
+          <t>521139</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -10159,12 +10159,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>15,7%</t>
+          <t>14,99%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>28,88%</t>
+          <t>29,09%</t>
         </is>
       </c>
     </row>
@@ -10187,12 +10187,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>141377</t>
+          <t>151068</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>348959</t>
+          <t>349655</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -10202,12 +10202,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>12,72%</t>
+          <t>13,59%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>31,39%</t>
+          <t>31,45%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -10222,12 +10222,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>128333</t>
+          <t>132020</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>176014</t>
+          <t>178819</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -10237,12 +10237,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>18,87%</t>
+          <t>19,42%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>25,89%</t>
+          <t>26,3%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -10257,12 +10257,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>274870</t>
+          <t>274798</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>501268</t>
+          <t>508982</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -10277,7 +10277,7 @@
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>27,98%</t>
+          <t>28,41%</t>
         </is>
       </c>
     </row>
@@ -10300,12 +10300,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>57141</t>
+          <t>64395</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>167672</t>
+          <t>167352</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -10315,12 +10315,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>5,14%</t>
+          <t>5,79%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>15,08%</t>
+          <t>15,05%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10335,12 +10335,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>107552</t>
+          <t>108295</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>224314</t>
+          <t>270483</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -10350,12 +10350,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>15,82%</t>
+          <t>15,93%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>32,99%</t>
+          <t>39,78%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10370,12 +10370,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>176954</t>
+          <t>177949</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>340322</t>
+          <t>356306</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -10385,12 +10385,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>9,88%</t>
+          <t>9,93%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>19,0%</t>
+          <t>19,89%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P6605-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P6605-Estudios-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>79463</t>
+          <t>80271</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>113388</t>
+          <t>114051</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>21,16%</t>
+          <t>21,38%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>30,19%</t>
+          <t>30,37%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>31354</t>
+          <t>30708</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>52614</t>
+          <t>53610</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>20,56%</t>
+          <t>20,14%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>34,51%</t>
+          <t>35,16%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>117874</t>
+          <t>115282</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>156654</t>
+          <t>156371</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>22,33%</t>
+          <t>21,83%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>29,67%</t>
+          <t>29,62%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>42870</t>
+          <t>41871</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>71011</t>
+          <t>69412</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>11,42%</t>
+          <t>11,15%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>18,91%</t>
+          <t>18,48%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>18072</t>
+          <t>18053</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>37062</t>
+          <t>37333</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>11,85%</t>
+          <t>11,84%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>24,31%</t>
+          <t>24,49%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>65438</t>
+          <t>64772</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>98881</t>
+          <t>100836</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>12,39%</t>
+          <t>12,27%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>18,73%</t>
+          <t>19,1%</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>106920</t>
+          <t>107086</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>143480</t>
+          <t>142862</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>28,47%</t>
+          <t>28,52%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>38,21%</t>
+          <t>38,04%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>26963</t>
+          <t>26953</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>47501</t>
+          <t>48659</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1014,7 +1014,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>31,15%</t>
+          <t>31,91%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>140911</t>
+          <t>140829</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>184535</t>
+          <t>184266</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>26,69%</t>
+          <t>26,67%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>34,95%</t>
+          <t>34,9%</t>
         </is>
       </c>
     </row>
@@ -1072,12 +1072,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>82106</t>
+          <t>83572</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>118121</t>
+          <t>118481</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1087,12 +1087,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>21,86%</t>
+          <t>22,25%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>31,46%</t>
+          <t>31,55%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>36312</t>
+          <t>36530</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>60269</t>
+          <t>59958</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1122,12 +1122,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>23,82%</t>
+          <t>23,96%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>39,53%</t>
+          <t>39,33%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1142,12 +1142,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>125687</t>
+          <t>127028</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>166627</t>
+          <t>170651</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>23,8%</t>
+          <t>24,06%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>31,56%</t>
+          <t>32,32%</t>
         </is>
       </c>
     </row>
@@ -1302,12 +1302,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>239050</t>
+          <t>240539</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>295037</t>
+          <t>295723</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1317,12 +1317,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>21,31%</t>
+          <t>21,44%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>26,3%</t>
+          <t>26,36%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1337,12 +1337,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>143917</t>
+          <t>143765</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>186941</t>
+          <t>186439</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1352,12 +1352,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>24,78%</t>
+          <t>24,76%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>32,19%</t>
+          <t>32,11%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1372,12 +1372,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>395336</t>
+          <t>398116</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>468521</t>
+          <t>464175</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1387,12 +1387,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>23,22%</t>
+          <t>23,38%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>27,52%</t>
+          <t>27,26%</t>
         </is>
       </c>
     </row>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>232112</t>
+          <t>231686</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>292303</t>
+          <t>288249</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1430,12 +1430,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>20,69%</t>
+          <t>20,65%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>26,05%</t>
+          <t>25,69%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1450,12 +1450,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>113509</t>
+          <t>113838</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>156147</t>
+          <t>155627</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1465,12 +1465,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>19,55%</t>
+          <t>19,6%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>26,89%</t>
+          <t>26,8%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>357079</t>
+          <t>357960</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>427447</t>
+          <t>427867</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>20,97%</t>
+          <t>21,02%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>25,1%</t>
+          <t>25,13%</t>
         </is>
       </c>
     </row>
@@ -1528,12 +1528,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>270806</t>
+          <t>273161</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>329977</t>
+          <t>331510</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1543,12 +1543,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>24,14%</t>
+          <t>24,35%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>29,41%</t>
+          <t>29,55%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1563,12 +1563,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>139677</t>
+          <t>142999</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>185865</t>
+          <t>184297</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1578,12 +1578,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>24,05%</t>
+          <t>24,63%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>32,01%</t>
+          <t>31,74%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1598,12 +1598,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>428571</t>
+          <t>429367</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>502037</t>
+          <t>507207</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1613,12 +1613,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>25,17%</t>
+          <t>25,22%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>29,48%</t>
+          <t>29,79%</t>
         </is>
       </c>
     </row>
@@ -1641,12 +1641,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>265558</t>
+          <t>264699</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>324381</t>
+          <t>324808</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1656,12 +1656,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>23,67%</t>
+          <t>23,59%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>28,91%</t>
+          <t>28,95%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1676,12 +1676,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>101541</t>
+          <t>101943</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>141213</t>
+          <t>142740</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1691,12 +1691,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>17,49%</t>
+          <t>17,56%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>24,32%</t>
+          <t>24,58%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1711,12 +1711,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>380314</t>
+          <t>374972</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>451250</t>
+          <t>451470</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1726,12 +1726,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>22,34%</t>
+          <t>22,02%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>26,5%</t>
+          <t>26,51%</t>
         </is>
       </c>
     </row>
@@ -1871,12 +1871,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>135910</t>
+          <t>137811</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>177622</t>
+          <t>178087</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1886,12 +1886,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>33,61%</t>
+          <t>34,08%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>43,93%</t>
+          <t>44,04%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1906,12 +1906,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>92832</t>
+          <t>93007</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>125651</t>
+          <t>127455</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1921,12 +1921,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>31,99%</t>
+          <t>32,05%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>43,3%</t>
+          <t>43,92%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1941,12 +1941,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>241163</t>
+          <t>240199</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>294865</t>
+          <t>291924</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1956,12 +1956,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>34,72%</t>
+          <t>34,58%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>42,46%</t>
+          <t>42,03%</t>
         </is>
       </c>
     </row>
@@ -1984,12 +1984,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>104521</t>
+          <t>105005</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>144906</t>
+          <t>143692</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1999,12 +1999,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>25,85%</t>
+          <t>25,97%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>35,84%</t>
+          <t>35,54%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2019,12 +2019,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>71104</t>
+          <t>70757</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>102207</t>
+          <t>102068</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2034,12 +2034,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>24,5%</t>
+          <t>24,38%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>35,22%</t>
+          <t>35,17%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2054,12 +2054,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>185300</t>
+          <t>185466</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>235487</t>
+          <t>236673</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2069,12 +2069,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>26,68%</t>
+          <t>26,7%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>33,91%</t>
+          <t>34,08%</t>
         </is>
       </c>
     </row>
@@ -2097,12 +2097,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>60801</t>
+          <t>59990</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>93540</t>
+          <t>92373</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2112,12 +2112,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>15,04%</t>
+          <t>14,84%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>23,13%</t>
+          <t>22,85%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2132,12 +2132,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>59641</t>
+          <t>61217</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>88546</t>
+          <t>90784</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2147,12 +2147,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>20,55%</t>
+          <t>21,1%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>30,51%</t>
+          <t>31,29%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,12 +2167,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>127653</t>
+          <t>126315</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>172361</t>
+          <t>172104</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2182,12 +2182,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>18,38%</t>
+          <t>18,19%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>24,82%</t>
+          <t>24,78%</t>
         </is>
       </c>
     </row>
@@ -2210,12 +2210,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>34975</t>
+          <t>36019</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>63264</t>
+          <t>63119</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2225,12 +2225,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>8,65%</t>
+          <t>8,91%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>15,65%</t>
+          <t>15,61%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2245,12 +2245,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>12647</t>
+          <t>12984</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>31294</t>
+          <t>30400</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2260,12 +2260,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>4,36%</t>
+          <t>4,47%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>10,78%</t>
+          <t>10,48%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,12 +2280,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>54644</t>
+          <t>54101</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>88810</t>
+          <t>85247</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2295,12 +2295,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>7,87%</t>
+          <t>7,79%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>12,79%</t>
+          <t>12,27%</t>
         </is>
       </c>
     </row>
@@ -2440,12 +2440,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>484338</t>
+          <t>478224</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>561022</t>
+          <t>559312</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2455,12 +2455,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>25,47%</t>
+          <t>25,14%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>29,5%</t>
+          <t>29,41%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2475,12 +2475,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>287696</t>
+          <t>286154</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>346778</t>
+          <t>346328</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2490,12 +2490,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>28,11%</t>
+          <t>27,96%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>33,89%</t>
+          <t>33,84%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2510,12 +2510,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>788231</t>
+          <t>791048</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>888929</t>
+          <t>888102</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2525,12 +2525,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>26,95%</t>
+          <t>27,04%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>30,39%</t>
+          <t>30,36%</t>
         </is>
       </c>
     </row>
@@ -2553,12 +2553,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>400897</t>
+          <t>404142</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>475390</t>
+          <t>474413</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2568,12 +2568,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>21,08%</t>
+          <t>21,25%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>25,0%</t>
+          <t>24,94%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2588,12 +2588,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>218532</t>
+          <t>222120</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>275727</t>
+          <t>272839</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2603,12 +2603,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>21,35%</t>
+          <t>21,71%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>26,94%</t>
+          <t>26,66%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2623,12 +2623,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>637632</t>
+          <t>637017</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>734217</t>
+          <t>731039</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2638,12 +2638,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>21,8%</t>
+          <t>21,78%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>25,1%</t>
+          <t>24,99%</t>
         </is>
       </c>
     </row>
@@ -2666,12 +2666,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>465505</t>
+          <t>465842</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>541781</t>
+          <t>540784</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2681,12 +2681,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>24,48%</t>
+          <t>24,49%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>28,49%</t>
+          <t>28,43%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2701,12 +2701,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>245867</t>
+          <t>242177</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>300873</t>
+          <t>301902</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2716,12 +2716,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>24,03%</t>
+          <t>23,67%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>29,4%</t>
+          <t>29,5%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2736,12 +2736,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>724939</t>
+          <t>726680</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>825722</t>
+          <t>826448</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2751,12 +2751,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>24,78%</t>
+          <t>24,84%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>28,23%</t>
+          <t>28,25%</t>
         </is>
       </c>
     </row>
@@ -2779,12 +2779,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>408239</t>
+          <t>405585</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>480945</t>
+          <t>482468</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2794,12 +2794,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>21,47%</t>
+          <t>21,33%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>25,29%</t>
+          <t>25,37%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2814,12 +2814,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>162162</t>
+          <t>162820</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>212380</t>
+          <t>213322</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2829,12 +2829,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>15,85%</t>
+          <t>15,91%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>20,75%</t>
+          <t>20,85%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2849,12 +2849,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>584980</t>
+          <t>585698</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>676047</t>
+          <t>674317</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2864,12 +2864,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>20,0%</t>
+          <t>20,02%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>23,11%</t>
+          <t>23,05%</t>
         </is>
       </c>
     </row>
@@ -3240,12 +3240,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>17440</t>
+          <t>17760</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>37773</t>
+          <t>36991</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3255,12 +3255,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>9,59%</t>
+          <t>9,76%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>20,77%</t>
+          <t>20,33%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3275,12 +3275,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>22164</t>
+          <t>22724</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>44314</t>
+          <t>43307</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3290,12 +3290,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>15,83%</t>
+          <t>16,23%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>31,66%</t>
+          <t>30,94%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3310,12 +3310,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>46092</t>
+          <t>44279</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>74482</t>
+          <t>72966</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3325,12 +3325,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>14,32%</t>
+          <t>13,76%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>23,14%</t>
+          <t>22,67%</t>
         </is>
       </c>
     </row>
@@ -3353,12 +3353,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>26993</t>
+          <t>27888</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>49495</t>
+          <t>50252</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3368,12 +3368,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>14,84%</t>
+          <t>15,33%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>27,21%</t>
+          <t>27,62%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3388,12 +3388,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>32134</t>
+          <t>34395</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>54414</t>
+          <t>55835</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3403,12 +3403,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>22,96%</t>
+          <t>24,57%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>38,87%</t>
+          <t>39,89%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3423,12 +3423,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>65732</t>
+          <t>67344</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>97677</t>
+          <t>100576</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3438,12 +3438,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>20,42%</t>
+          <t>20,92%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>30,35%</t>
+          <t>31,25%</t>
         </is>
       </c>
     </row>
@@ -3466,12 +3466,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>57460</t>
+          <t>57477</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>85674</t>
+          <t>83209</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3481,12 +3481,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>31,59%</t>
+          <t>31,6%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>47,1%</t>
+          <t>45,74%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -3501,12 +3501,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>15251</t>
+          <t>15372</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>33104</t>
+          <t>33108</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3516,7 +3516,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>10,9%</t>
+          <t>10,98%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -3536,12 +3536,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>77509</t>
+          <t>76278</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>109922</t>
+          <t>107969</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -3551,12 +3551,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>24,08%</t>
+          <t>23,7%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>34,15%</t>
+          <t>33,54%</t>
         </is>
       </c>
     </row>
@@ -3579,12 +3579,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>36808</t>
+          <t>35917</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>61833</t>
+          <t>59552</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3594,12 +3594,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>20,23%</t>
+          <t>19,74%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>33,99%</t>
+          <t>32,74%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3614,12 +3614,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>31344</t>
+          <t>31297</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>52784</t>
+          <t>53241</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3629,12 +3629,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>22,39%</t>
+          <t>22,36%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>37,71%</t>
+          <t>38,04%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3649,12 +3649,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>73347</t>
+          <t>72727</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>106844</t>
+          <t>106846</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3664,7 +3664,7 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>22,79%</t>
+          <t>22,59%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
@@ -3809,12 +3809,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>161525</t>
+          <t>162453</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>212334</t>
+          <t>215239</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -3824,12 +3824,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>17,71%</t>
+          <t>17,82%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>23,29%</t>
+          <t>23,61%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -3844,12 +3844,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>115133</t>
+          <t>115034</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>156616</t>
+          <t>156035</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3859,12 +3859,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>20,13%</t>
+          <t>20,12%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>27,39%</t>
+          <t>27,29%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -3879,12 +3879,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>291456</t>
+          <t>293268</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>360301</t>
+          <t>360480</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -3894,12 +3894,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>19,64%</t>
+          <t>19,77%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>24,28%</t>
+          <t>24,3%</t>
         </is>
       </c>
     </row>
@@ -3922,12 +3922,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>211009</t>
+          <t>212153</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>266136</t>
+          <t>266887</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3937,12 +3937,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>23,14%</t>
+          <t>23,27%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>29,19%</t>
+          <t>29,27%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3957,12 +3957,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>117293</t>
+          <t>117672</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>157107</t>
+          <t>158635</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3972,12 +3972,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>20,51%</t>
+          <t>20,58%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>27,47%</t>
+          <t>27,74%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3992,12 +3992,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>341888</t>
+          <t>340319</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>412270</t>
+          <t>411018</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4007,12 +4007,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>23,04%</t>
+          <t>22,94%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>27,79%</t>
+          <t>27,7%</t>
         </is>
       </c>
     </row>
@@ -4035,12 +4035,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>237966</t>
+          <t>240272</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>296447</t>
+          <t>297599</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4050,12 +4050,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>26,1%</t>
+          <t>26,35%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>32,51%</t>
+          <t>32,64%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4070,12 +4070,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>135907</t>
+          <t>135776</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>180513</t>
+          <t>180349</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4085,12 +4085,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>23,77%</t>
+          <t>23,74%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>31,57%</t>
+          <t>31,54%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4105,12 +4105,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>385463</t>
+          <t>391609</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>461633</t>
+          <t>464238</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4120,12 +4120,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>25,98%</t>
+          <t>26,39%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>31,11%</t>
+          <t>31,29%</t>
         </is>
       </c>
     </row>
@@ -4148,12 +4148,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>190042</t>
+          <t>193647</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>244554</t>
+          <t>243194</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -4163,12 +4163,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>20,84%</t>
+          <t>21,24%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>26,82%</t>
+          <t>26,67%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -4183,12 +4183,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>121873</t>
+          <t>121235</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>165762</t>
+          <t>162177</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4198,12 +4198,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>21,31%</t>
+          <t>21,2%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>28,99%</t>
+          <t>28,36%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -4218,12 +4218,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>323477</t>
+          <t>327380</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>392515</t>
+          <t>392907</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4233,12 +4233,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>21,8%</t>
+          <t>22,07%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>26,46%</t>
+          <t>26,48%</t>
         </is>
       </c>
     </row>
@@ -4378,12 +4378,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>95261</t>
+          <t>93415</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>130845</t>
+          <t>129709</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4393,12 +4393,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>30,12%</t>
+          <t>29,54%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>41,37%</t>
+          <t>41,01%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4413,12 +4413,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>67161</t>
+          <t>67696</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>97229</t>
+          <t>98682</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4428,12 +4428,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>28,59%</t>
+          <t>28,82%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>41,39%</t>
+          <t>42,01%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4448,12 +4448,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>169456</t>
+          <t>170346</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>217946</t>
+          <t>217362</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4463,12 +4463,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>30,75%</t>
+          <t>30,91%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>39,54%</t>
+          <t>39,44%</t>
         </is>
       </c>
     </row>
@@ -4491,12 +4491,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>54900</t>
+          <t>55943</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>87029</t>
+          <t>88630</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>17,36%</t>
+          <t>17,69%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>27,52%</t>
+          <t>28,02%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -4526,12 +4526,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>58732</t>
+          <t>58275</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>89325</t>
+          <t>88082</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -4541,12 +4541,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>25,0%</t>
+          <t>24,81%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>38,03%</t>
+          <t>37,5%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -4561,12 +4561,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>121075</t>
+          <t>122831</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>166787</t>
+          <t>166872</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -4576,12 +4576,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>21,97%</t>
+          <t>22,29%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>30,26%</t>
+          <t>30,28%</t>
         </is>
       </c>
     </row>
@@ -4604,12 +4604,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>68442</t>
+          <t>68551</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>102914</t>
+          <t>101535</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4619,12 +4619,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>21,64%</t>
+          <t>21,68%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>32,54%</t>
+          <t>32,11%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4639,12 +4639,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>42206</t>
+          <t>40576</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>69112</t>
+          <t>68504</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4654,12 +4654,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>17,97%</t>
+          <t>17,27%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>29,42%</t>
+          <t>29,16%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4674,12 +4674,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>115727</t>
+          <t>116490</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>161807</t>
+          <t>161594</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4689,12 +4689,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>21,0%</t>
+          <t>21,14%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>29,36%</t>
+          <t>29,32%</t>
         </is>
       </c>
     </row>
@@ -4717,12 +4717,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>37232</t>
+          <t>37350</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>64642</t>
+          <t>64268</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4732,12 +4732,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>11,77%</t>
+          <t>11,81%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>20,44%</t>
+          <t>20,32%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4752,12 +4752,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>17429</t>
+          <t>17476</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>37221</t>
+          <t>36005</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4767,12 +4767,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>7,42%</t>
+          <t>7,44%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>15,85%</t>
+          <t>15,33%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4787,12 +4787,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>59177</t>
+          <t>60534</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>94194</t>
+          <t>93102</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4802,12 +4802,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>10,74%</t>
+          <t>10,98%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>17,09%</t>
+          <t>16,89%</t>
         </is>
       </c>
     </row>
@@ -4947,12 +4947,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>293884</t>
+          <t>290531</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>359510</t>
+          <t>359531</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -4962,7 +4962,7 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>20,84%</t>
+          <t>20,61%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
@@ -4982,12 +4982,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>222884</t>
+          <t>222199</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>277835</t>
+          <t>279141</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -4997,12 +4997,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>23,54%</t>
+          <t>23,47%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>29,35%</t>
+          <t>29,48%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5017,12 +5017,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>529478</t>
+          <t>533280</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>618960</t>
+          <t>618561</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5032,12 +5032,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>22,47%</t>
+          <t>22,63%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>26,26%</t>
+          <t>26,25%</t>
         </is>
       </c>
     </row>
@@ -5060,12 +5060,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>314485</t>
+          <t>316195</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>379593</t>
+          <t>383160</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5075,12 +5075,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>22,3%</t>
+          <t>22,43%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>26,92%</t>
+          <t>27,17%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5095,12 +5095,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>224750</t>
+          <t>227162</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>281818</t>
+          <t>283141</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5110,12 +5110,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>23,74%</t>
+          <t>23,99%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>29,77%</t>
+          <t>29,91%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5130,12 +5130,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>562081</t>
+          <t>557797</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>651677</t>
+          <t>641690</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5145,12 +5145,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>23,85%</t>
+          <t>23,67%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>27,65%</t>
+          <t>27,23%</t>
         </is>
       </c>
     </row>
@@ -5173,12 +5173,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>387210</t>
+          <t>389286</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>456238</t>
+          <t>458259</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -5188,12 +5188,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>27,46%</t>
+          <t>27,61%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>32,36%</t>
+          <t>32,5%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -5208,12 +5208,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>207412</t>
+          <t>208729</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>264249</t>
+          <t>263686</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -5223,12 +5223,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>21,91%</t>
+          <t>22,05%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>27,91%</t>
+          <t>27,85%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -5243,12 +5243,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>612533</t>
+          <t>612066</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>701561</t>
+          <t>702065</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -5258,12 +5258,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>25,99%</t>
+          <t>25,97%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>29,77%</t>
+          <t>29,79%</t>
         </is>
       </c>
     </row>
@@ -5286,12 +5286,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>281556</t>
+          <t>284358</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>344706</t>
+          <t>348353</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5301,12 +5301,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>19,97%</t>
+          <t>20,17%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>24,45%</t>
+          <t>24,71%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5321,12 +5321,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>183609</t>
+          <t>185508</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>236719</t>
+          <t>239420</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5336,12 +5336,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>19,39%</t>
+          <t>19,59%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>25,0%</t>
+          <t>25,29%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5356,12 +5356,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>478292</t>
+          <t>483997</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>566602</t>
+          <t>569800</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5371,12 +5371,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>20,29%</t>
+          <t>20,54%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>24,04%</t>
+          <t>24,18%</t>
         </is>
       </c>
     </row>
@@ -5747,12 +5747,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>12907</t>
+          <t>12292</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>28994</t>
+          <t>28979</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5762,12 +5762,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>9,29%</t>
+          <t>8,85%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>20,88%</t>
+          <t>20,87%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5782,12 +5782,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>9961</t>
+          <t>10111</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>23309</t>
+          <t>24840</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5797,12 +5797,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>13,82%</t>
+          <t>14,03%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>32,34%</t>
+          <t>34,46%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5817,12 +5817,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>25536</t>
+          <t>26225</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>47055</t>
+          <t>48509</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5832,12 +5832,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>12,11%</t>
+          <t>12,43%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>22,31%</t>
+          <t>23,0%</t>
         </is>
       </c>
     </row>
@@ -5860,12 +5860,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>23958</t>
+          <t>23770</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>44858</t>
+          <t>45035</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5875,12 +5875,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>17,25%</t>
+          <t>17,12%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>32,3%</t>
+          <t>32,43%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5895,12 +5895,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>12447</t>
+          <t>13101</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>26456</t>
+          <t>27344</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5910,12 +5910,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>17,27%</t>
+          <t>18,17%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>36,7%</t>
+          <t>37,93%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5930,12 +5930,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>41320</t>
+          <t>40573</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>65814</t>
+          <t>67347</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5945,12 +5945,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>19,59%</t>
+          <t>19,23%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>31,2%</t>
+          <t>31,93%</t>
         </is>
       </c>
     </row>
@@ -5973,12 +5973,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>34165</t>
+          <t>33471</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>55863</t>
+          <t>56316</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5988,12 +5988,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>24,6%</t>
+          <t>24,1%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>40,23%</t>
+          <t>40,56%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -6008,12 +6008,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>11342</t>
+          <t>11677</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>26094</t>
+          <t>24923</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6023,12 +6023,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>15,73%</t>
+          <t>16,2%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>36,2%</t>
+          <t>34,57%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -6043,12 +6043,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>49500</t>
+          <t>48670</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>75507</t>
+          <t>74622</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6058,12 +6058,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>23,47%</t>
+          <t>23,07%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>35,79%</t>
+          <t>35,38%</t>
         </is>
       </c>
     </row>
@@ -6086,12 +6086,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>31111</t>
+          <t>30787</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>53980</t>
+          <t>53911</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6101,12 +6101,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>22,4%</t>
+          <t>22,17%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>38,87%</t>
+          <t>38,82%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6121,12 +6121,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>13229</t>
+          <t>12393</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>27637</t>
+          <t>26708</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6136,12 +6136,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>18,35%</t>
+          <t>17,19%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>38,34%</t>
+          <t>37,05%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6156,12 +6156,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>48758</t>
+          <t>48674</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>75423</t>
+          <t>75982</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6171,12 +6171,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>23,11%</t>
+          <t>23,07%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>35,75%</t>
+          <t>36,02%</t>
         </is>
       </c>
     </row>
@@ -6316,12 +6316,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>205493</t>
+          <t>207177</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>261195</t>
+          <t>260068</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -6331,12 +6331,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>22,3%</t>
+          <t>22,48%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>28,34%</t>
+          <t>28,22%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -6351,12 +6351,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>170084</t>
+          <t>169862</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>215458</t>
+          <t>217775</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -6366,12 +6366,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>26,13%</t>
+          <t>26,1%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>33,11%</t>
+          <t>33,46%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -6386,12 +6386,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>389324</t>
+          <t>390036</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>457557</t>
+          <t>460787</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -6401,12 +6401,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>24,76%</t>
+          <t>24,81%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>29,1%</t>
+          <t>29,31%</t>
         </is>
       </c>
     </row>
@@ -6429,12 +6429,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>200095</t>
+          <t>199951</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>256261</t>
+          <t>255518</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6444,12 +6444,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>21,71%</t>
+          <t>21,7%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>27,81%</t>
+          <t>27,73%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6464,12 +6464,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>151756</t>
+          <t>150864</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>196561</t>
+          <t>196158</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6479,12 +6479,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>23,32%</t>
+          <t>23,18%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>30,2%</t>
+          <t>30,14%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6499,12 +6499,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>365503</t>
+          <t>368467</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>435841</t>
+          <t>438414</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6514,12 +6514,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>23,25%</t>
+          <t>23,43%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>27,72%</t>
+          <t>27,88%</t>
         </is>
       </c>
     </row>
@@ -6542,12 +6542,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>250646</t>
+          <t>248978</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>308536</t>
+          <t>305821</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6557,12 +6557,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>27,2%</t>
+          <t>27,02%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>33,48%</t>
+          <t>33,19%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6577,12 +6577,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>126759</t>
+          <t>128309</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>168759</t>
+          <t>172453</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6592,12 +6592,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>19,48%</t>
+          <t>19,72%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>25,93%</t>
+          <t>26,5%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6612,12 +6612,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>393584</t>
+          <t>390462</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>465778</t>
+          <t>459007</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6627,12 +6627,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>25,03%</t>
+          <t>24,83%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>29,62%</t>
+          <t>29,19%</t>
         </is>
       </c>
     </row>
@@ -6655,12 +6655,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>161080</t>
+          <t>161815</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>213609</t>
+          <t>213125</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -6670,12 +6670,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>17,48%</t>
+          <t>17,56%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>23,18%</t>
+          <t>23,13%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -6690,12 +6690,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>115353</t>
+          <t>114475</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>157383</t>
+          <t>156840</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6705,12 +6705,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>17,72%</t>
+          <t>17,59%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>24,18%</t>
+          <t>24,1%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -6725,12 +6725,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>288072</t>
+          <t>286918</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>354940</t>
+          <t>355753</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6740,12 +6740,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>18,32%</t>
+          <t>18,25%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>22,57%</t>
+          <t>22,63%</t>
         </is>
       </c>
     </row>
@@ -6885,12 +6885,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>141758</t>
+          <t>141988</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>180956</t>
+          <t>180408</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6900,12 +6900,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>40,65%</t>
+          <t>40,72%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>51,89%</t>
+          <t>51,74%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6920,12 +6920,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>113167</t>
+          <t>111334</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>146263</t>
+          <t>146419</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6935,12 +6935,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>36,81%</t>
+          <t>36,21%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>47,57%</t>
+          <t>47,62%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6955,12 +6955,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>261620</t>
+          <t>262239</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>313298</t>
+          <t>314800</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6970,12 +6970,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>39,87%</t>
+          <t>39,97%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>47,75%</t>
+          <t>47,98%</t>
         </is>
       </c>
     </row>
@@ -6998,12 +6998,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>70482</t>
+          <t>71596</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>104244</t>
+          <t>107143</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -7013,12 +7013,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>20,21%</t>
+          <t>20,53%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>29,89%</t>
+          <t>30,73%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -7033,12 +7033,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>52253</t>
+          <t>52685</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>82228</t>
+          <t>82775</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -7048,12 +7048,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>17,0%</t>
+          <t>17,14%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>26,75%</t>
+          <t>26,92%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -7068,12 +7068,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>134176</t>
+          <t>134052</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>178326</t>
+          <t>175917</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -7083,12 +7083,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>20,45%</t>
+          <t>20,43%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>27,18%</t>
+          <t>26,81%</t>
         </is>
       </c>
     </row>
@@ -7111,12 +7111,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>46218</t>
+          <t>46000</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>74980</t>
+          <t>75479</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7126,12 +7126,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>13,25%</t>
+          <t>13,19%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>21,5%</t>
+          <t>21,65%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7146,12 +7146,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>49639</t>
+          <t>48337</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>75378</t>
+          <t>76469</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7161,12 +7161,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>16,15%</t>
+          <t>15,72%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>24,52%</t>
+          <t>24,87%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7181,12 +7181,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>102136</t>
+          <t>99975</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>141625</t>
+          <t>142707</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7196,12 +7196,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>15,57%</t>
+          <t>15,24%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>21,58%</t>
+          <t>21,75%</t>
         </is>
       </c>
     </row>
@@ -7224,12 +7224,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>30257</t>
+          <t>31359</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>55932</t>
+          <t>55904</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7239,12 +7239,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>8,68%</t>
+          <t>8,99%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>16,04%</t>
+          <t>16,03%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7259,12 +7259,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>38010</t>
+          <t>37404</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>64230</t>
+          <t>65431</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7274,12 +7274,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>12,36%</t>
+          <t>12,17%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>20,89%</t>
+          <t>21,28%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7294,12 +7294,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>74864</t>
+          <t>76133</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>111490</t>
+          <t>111016</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7309,12 +7309,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>11,41%</t>
+          <t>11,6%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>16,99%</t>
+          <t>16,92%</t>
         </is>
       </c>
     </row>
@@ -7454,12 +7454,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>376093</t>
+          <t>377440</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>447512</t>
+          <t>443385</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -7469,12 +7469,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>26,69%</t>
+          <t>26,79%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>31,76%</t>
+          <t>31,47%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7489,12 +7489,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>308561</t>
+          <t>310542</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>369517</t>
+          <t>367515</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7504,12 +7504,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>29,95%</t>
+          <t>30,14%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>35,86%</t>
+          <t>35,67%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7524,12 +7524,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>704975</t>
+          <t>700959</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>793587</t>
+          <t>794426</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7539,12 +7539,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>28,9%</t>
+          <t>28,73%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>32,53%</t>
+          <t>32,57%</t>
         </is>
       </c>
     </row>
@@ -7567,12 +7567,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>316966</t>
+          <t>317822</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>384727</t>
+          <t>381083</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7582,12 +7582,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>22,49%</t>
+          <t>22,56%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>27,3%</t>
+          <t>27,05%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7602,12 +7602,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>232180</t>
+          <t>233569</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>287029</t>
+          <t>288926</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7617,12 +7617,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>22,53%</t>
+          <t>22,67%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>27,86%</t>
+          <t>28,04%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7637,12 +7637,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>562986</t>
+          <t>564291</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>649322</t>
+          <t>651904</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7652,12 +7652,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>23,08%</t>
+          <t>23,13%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>26,62%</t>
+          <t>26,72%</t>
         </is>
       </c>
     </row>
@@ -7680,12 +7680,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>346452</t>
+          <t>346928</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>413524</t>
+          <t>415089</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -7695,12 +7695,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>24,59%</t>
+          <t>24,62%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>29,35%</t>
+          <t>29,46%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -7715,12 +7715,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>200573</t>
+          <t>201899</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>251980</t>
+          <t>255926</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -7730,12 +7730,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>19,47%</t>
+          <t>19,6%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>24,46%</t>
+          <t>24,84%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -7750,12 +7750,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>565806</t>
+          <t>561887</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>653356</t>
+          <t>651008</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -7765,12 +7765,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>23,19%</t>
+          <t>23,03%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>26,78%</t>
+          <t>26,69%</t>
         </is>
       </c>
     </row>
@@ -7793,12 +7793,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>240356</t>
+          <t>239430</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>302036</t>
+          <t>303978</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -7808,12 +7808,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>17,06%</t>
+          <t>16,99%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>21,44%</t>
+          <t>21,57%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -7828,12 +7828,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>178451</t>
+          <t>180061</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>230889</t>
+          <t>231951</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -7843,12 +7843,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>17,32%</t>
+          <t>17,48%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>22,41%</t>
+          <t>22,51%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -7863,12 +7863,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>438985</t>
+          <t>434849</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>515423</t>
+          <t>518148</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -7878,12 +7878,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>18,0%</t>
+          <t>17,83%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>21,13%</t>
+          <t>21,24%</t>
         </is>
       </c>
     </row>
@@ -8249,32 +8249,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>12406</t>
+          <t>13007</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>7067</t>
+          <t>6772</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>21359</t>
+          <t>23302</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>18,97%</t>
+          <t>14,79%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>10,8%</t>
+          <t>7,7%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>32,65%</t>
+          <t>26,49%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8284,32 +8284,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>3711</t>
+          <t>4873</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1472</t>
+          <t>2174</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>7685</t>
+          <t>9225</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>9,48%</t>
+          <t>10,55%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>3,76%</t>
+          <t>4,71%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>19,64%</t>
+          <t>19,98%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8319,32 +8319,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>16117</t>
+          <t>17880</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>9325</t>
+          <t>11026</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>25231</t>
+          <t>28023</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>15,42%</t>
+          <t>13,33%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>8,92%</t>
+          <t>8,22%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>24,14%</t>
+          <t>20,89%</t>
         </is>
       </c>
     </row>
@@ -8362,32 +8362,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>8402</t>
+          <t>11206</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>4030</t>
+          <t>5309</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>14863</t>
+          <t>18676</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>12,84%</t>
+          <t>12,74%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>6,16%</t>
+          <t>6,04%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>22,72%</t>
+          <t>21,23%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8397,32 +8397,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>13827</t>
+          <t>15549</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>8986</t>
+          <t>10419</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>18407</t>
+          <t>20813</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>35,34%</t>
+          <t>33,67%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>22,97%</t>
+          <t>22,56%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>47,05%</t>
+          <t>45,07%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8432,32 +8432,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>22229</t>
+          <t>26755</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>15761</t>
+          <t>18677</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>30646</t>
+          <t>36202</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>21,26%</t>
+          <t>19,95%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>15,08%</t>
+          <t>13,92%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>29,32%</t>
+          <t>26,99%</t>
         </is>
       </c>
     </row>
@@ -8475,32 +8475,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>26198</t>
+          <t>32076</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>17868</t>
+          <t>22358</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>35550</t>
+          <t>43704</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>40,05%</t>
+          <t>36,47%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>27,32%</t>
+          <t>25,42%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>54,35%</t>
+          <t>49,69%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -8510,32 +8510,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>11991</t>
+          <t>14689</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>7801</t>
+          <t>9792</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>17285</t>
+          <t>20797</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>30,65%</t>
+          <t>31,81%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>19,94%</t>
+          <t>21,21%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>44,18%</t>
+          <t>45,04%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -8545,32 +8545,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>38189</t>
+          <t>46765</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>28942</t>
+          <t>35708</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>48411</t>
+          <t>59055</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>36,53%</t>
+          <t>34,87%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>27,69%</t>
+          <t>26,62%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>46,31%</t>
+          <t>44,03%</t>
         </is>
       </c>
     </row>
@@ -8588,32 +8588,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>18409</t>
+          <t>31664</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>11749</t>
+          <t>21294</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>26167</t>
+          <t>43168</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>28,14%</t>
+          <t>36,0%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>17,96%</t>
+          <t>24,21%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>40,0%</t>
+          <t>49,08%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -8623,32 +8623,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>9594</t>
+          <t>11066</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>5554</t>
+          <t>6628</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>14954</t>
+          <t>17130</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>24,52%</t>
+          <t>23,96%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>14,2%</t>
+          <t>14,35%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>38,22%</t>
+          <t>37,1%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -8658,32 +8658,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>28003</t>
+          <t>42730</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>20206</t>
+          <t>30488</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>38224</t>
+          <t>55702</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>26,79%</t>
+          <t>31,86%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>19,33%</t>
+          <t>22,73%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>36,57%</t>
+          <t>41,53%</t>
         </is>
       </c>
     </row>
@@ -8701,17 +8701,17 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>65414</t>
+          <t>87953</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>65414</t>
+          <t>87953</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>65414</t>
+          <t>87953</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -8736,17 +8736,17 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>39123</t>
+          <t>46176</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>39123</t>
+          <t>46176</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>39123</t>
+          <t>46176</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -8771,17 +8771,17 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>104537</t>
+          <t>134129</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>104537</t>
+          <t>134129</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>104537</t>
+          <t>134129</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -8818,32 +8818,32 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>344018</t>
+          <t>113675</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>134501</t>
+          <t>92834</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>611633</t>
+          <t>135733</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>42,78%</t>
+          <t>18,34%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>16,73%</t>
+          <t>14,98%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>76,06%</t>
+          <t>21,9%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -8853,32 +8853,32 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>90885</t>
+          <t>103174</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>68871</t>
+          <t>85538</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>110224</t>
+          <t>119945</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>20,57%</t>
+          <t>22,69%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>15,59%</t>
+          <t>18,81%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>24,95%</t>
+          <t>26,38%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -8888,32 +8888,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>434904</t>
+          <t>216849</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>223618</t>
+          <t>190126</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>826867</t>
+          <t>245927</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>34,91%</t>
+          <t>20,18%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>17,95%</t>
+          <t>17,69%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>66,36%</t>
+          <t>22,89%</t>
         </is>
       </c>
     </row>
@@ -8931,32 +8931,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>174359</t>
+          <t>182851</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>72920</t>
+          <t>158314</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>261003</t>
+          <t>207444</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>21,68%</t>
+          <t>29,5%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>9,07%</t>
+          <t>25,54%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>32,46%</t>
+          <t>33,47%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8966,32 +8966,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>126640</t>
+          <t>136805</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>98611</t>
+          <t>121498</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>146292</t>
+          <t>154764</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>28,67%</t>
+          <t>30,09%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>22,32%</t>
+          <t>26,72%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>33,12%</t>
+          <t>34,04%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -9001,32 +9001,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>300998</t>
+          <t>319655</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>153430</t>
+          <t>286712</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>389598</t>
+          <t>349370</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>24,16%</t>
+          <t>29,75%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>12,31%</t>
+          <t>26,68%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>31,27%</t>
+          <t>32,51%</t>
         </is>
       </c>
     </row>
@@ -9044,32 +9044,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>199993</t>
+          <t>220092</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>81763</t>
+          <t>191424</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>300892</t>
+          <t>246705</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>24,87%</t>
+          <t>35,51%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>10,17%</t>
+          <t>30,88%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>37,42%</t>
+          <t>39,8%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -9079,32 +9079,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>113587</t>
+          <t>127131</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>88047</t>
+          <t>109360</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>131871</t>
+          <t>144692</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>25,71%</t>
+          <t>27,96%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>19,93%</t>
+          <t>24,05%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>29,85%</t>
+          <t>31,82%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -9114,32 +9114,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>313580</t>
+          <t>347223</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>151401</t>
+          <t>315433</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>407290</t>
+          <t>380710</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>25,17%</t>
+          <t>32,31%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>12,15%</t>
+          <t>29,36%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>32,69%</t>
+          <t>35,43%</t>
         </is>
       </c>
     </row>
@@ -9157,32 +9157,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>85821</t>
+          <t>103193</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>35129</t>
+          <t>84157</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>132229</t>
+          <t>128830</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>10,67%</t>
+          <t>16,65%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>4,37%</t>
+          <t>13,58%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>16,44%</t>
+          <t>20,79%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -9192,32 +9192,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>110643</t>
+          <t>87610</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>78636</t>
+          <t>72693</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>184383</t>
+          <t>104284</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>25,05%</t>
+          <t>19,27%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>17,8%</t>
+          <t>15,99%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>41,74%</t>
+          <t>22,93%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -9227,32 +9227,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>196464</t>
+          <t>190803</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>110685</t>
+          <t>165544</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>284162</t>
+          <t>220561</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>15,77%</t>
+          <t>17,76%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>8,88%</t>
+          <t>15,41%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>22,81%</t>
+          <t>20,53%</t>
         </is>
       </c>
     </row>
@@ -9270,17 +9270,17 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>804191</t>
+          <t>619811</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>804191</t>
+          <t>619811</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>804191</t>
+          <t>619811</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -9305,17 +9305,17 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>441755</t>
+          <t>454719</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>441755</t>
+          <t>454719</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>441755</t>
+          <t>454719</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -9340,17 +9340,17 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>1245946</t>
+          <t>1074530</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1245946</t>
+          <t>1074530</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1245946</t>
+          <t>1074530</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -9387,32 +9387,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>130856</t>
+          <t>152310</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>113711</t>
+          <t>133461</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>146043</t>
+          <t>169165</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>54,06%</t>
+          <t>56,8%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>46,98%</t>
+          <t>49,77%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>60,33%</t>
+          <t>63,09%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9422,32 +9422,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>91692</t>
+          <t>103240</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>79232</t>
+          <t>90887</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>104240</t>
+          <t>117470</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>46,06%</t>
+          <t>47,04%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>39,8%</t>
+          <t>41,41%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>52,36%</t>
+          <t>53,52%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9457,32 +9457,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>222549</t>
+          <t>255549</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>202345</t>
+          <t>232347</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>242722</t>
+          <t>278161</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>50,45%</t>
+          <t>52,41%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>45,87%</t>
+          <t>47,65%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>55,02%</t>
+          <t>57,05%</t>
         </is>
       </c>
     </row>
@@ -9500,32 +9500,32 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>52817</t>
+          <t>55915</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>39923</t>
+          <t>41199</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>66626</t>
+          <t>71092</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>21,82%</t>
+          <t>20,85%</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>16,49%</t>
+          <t>15,37%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>27,52%</t>
+          <t>26,51%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -9535,32 +9535,32 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>55461</t>
+          <t>61069</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>44828</t>
+          <t>49366</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>65792</t>
+          <t>72401</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>27,86%</t>
+          <t>27,82%</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>22,52%</t>
+          <t>22,49%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>33,05%</t>
+          <t>32,99%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -9570,32 +9570,32 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>108278</t>
+          <t>116984</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>91652</t>
+          <t>99979</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>125478</t>
+          <t>136834</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
         <is>
-          <t>24,55%</t>
+          <t>23,99%</t>
         </is>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>20,78%</t>
+          <t>20,5%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>28,45%</t>
+          <t>28,06%</t>
         </is>
       </c>
     </row>
@@ -9613,32 +9613,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>38190</t>
+          <t>38533</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>27501</t>
+          <t>28072</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>51181</t>
+          <t>51041</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>15,78%</t>
+          <t>14,37%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>11,36%</t>
+          <t>10,47%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>21,14%</t>
+          <t>19,04%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -9648,32 +9648,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>31037</t>
+          <t>31275</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>22697</t>
+          <t>22901</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>42384</t>
+          <t>41789</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>15,59%</t>
+          <t>14,25%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>11,4%</t>
+          <t>10,43%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>21,29%</t>
+          <t>19,04%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -9683,32 +9683,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>69227</t>
+          <t>69808</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>55470</t>
+          <t>56097</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>84896</t>
+          <t>87503</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>15,69%</t>
+          <t>14,32%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>12,57%</t>
+          <t>11,5%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>19,25%</t>
+          <t>17,94%</t>
         </is>
       </c>
     </row>
@@ -9726,32 +9726,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>20195</t>
+          <t>21376</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>11095</t>
+          <t>12612</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>34394</t>
+          <t>38036</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>8,34%</t>
+          <t>7,97%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>4,58%</t>
+          <t>4,7%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>14,21%</t>
+          <t>14,19%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -9761,32 +9761,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>20876</t>
+          <t>23900</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>13853</t>
+          <t>16500</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>30679</t>
+          <t>33685</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>10,49%</t>
+          <t>10,89%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>6,96%</t>
+          <t>7,52%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>15,41%</t>
+          <t>15,35%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -9796,32 +9796,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>41071</t>
+          <t>45276</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>29848</t>
+          <t>32487</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>57771</t>
+          <t>64496</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>9,31%</t>
+          <t>9,29%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>6,77%</t>
+          <t>6,66%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>13,1%</t>
+          <t>13,23%</t>
         </is>
       </c>
     </row>
@@ -9839,17 +9839,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>242059</t>
+          <t>268134</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>242059</t>
+          <t>268134</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>242059</t>
+          <t>268134</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -9874,17 +9874,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>199066</t>
+          <t>219483</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>199066</t>
+          <t>219483</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>199066</t>
+          <t>219483</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -9909,17 +9909,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>441125</t>
+          <t>487617</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>441125</t>
+          <t>487617</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>441125</t>
+          <t>487617</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -9956,32 +9956,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>487280</t>
+          <t>278991</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>301580</t>
+          <t>246805</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>754875</t>
+          <t>313782</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>43,83%</t>
+          <t>28,59%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>27,13%</t>
+          <t>25,29%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>67,91%</t>
+          <t>32,15%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9991,32 +9991,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>186288</t>
+          <t>211286</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>154409</t>
+          <t>189409</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>208309</t>
+          <t>232743</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>27,4%</t>
+          <t>29,33%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>22,71%</t>
+          <t>26,29%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>30,64%</t>
+          <t>32,31%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -10026,32 +10026,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>673568</t>
+          <t>490278</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>477892</t>
+          <t>450983</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>1086206</t>
+          <t>527423</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>37,6%</t>
+          <t>28,9%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>26,67%</t>
+          <t>26,59%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>60,63%</t>
+          <t>31,09%</t>
         </is>
       </c>
     </row>
@@ -10069,32 +10069,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>235577</t>
+          <t>249972</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>129714</t>
+          <t>222552</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>312963</t>
+          <t>282620</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>21,19%</t>
+          <t>25,61%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>11,67%</t>
+          <t>22,8%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>28,15%</t>
+          <t>28,96%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -10104,32 +10104,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>195928</t>
+          <t>213423</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>164478</t>
+          <t>195177</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>218446</t>
+          <t>236940</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>28,82%</t>
+          <t>29,63%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>24,19%</t>
+          <t>27,09%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>32,13%</t>
+          <t>32,89%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -10139,32 +10139,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>431505</t>
+          <t>463395</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>268649</t>
+          <t>427290</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>521139</t>
+          <t>500835</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>24,08%</t>
+          <t>27,32%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>14,99%</t>
+          <t>25,19%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>29,09%</t>
+          <t>29,53%</t>
         </is>
       </c>
     </row>
@@ -10182,32 +10182,32 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>264380</t>
+          <t>290701</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>151068</t>
+          <t>256438</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>349655</t>
+          <t>322981</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>23,78%</t>
+          <t>29,79%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>13,59%</t>
+          <t>26,28%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>31,45%</t>
+          <t>33,1%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -10217,32 +10217,32 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>156615</t>
+          <t>173094</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>132020</t>
+          <t>153341</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>178819</t>
+          <t>194872</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>23,03%</t>
+          <t>24,03%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>19,42%</t>
+          <t>21,29%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>26,3%</t>
+          <t>27,05%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -10252,32 +10252,32 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>420995</t>
+          <t>463795</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>274798</t>
+          <t>428508</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>508982</t>
+          <t>503984</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>23,5%</t>
+          <t>27,34%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>15,34%</t>
+          <t>25,26%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>28,41%</t>
+          <t>29,71%</t>
         </is>
       </c>
     </row>
@@ -10295,32 +10295,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>124425</t>
+          <t>156233</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>64395</t>
+          <t>127199</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>167352</t>
+          <t>185963</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>11,19%</t>
+          <t>16,01%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>5,79%</t>
+          <t>13,03%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>15,05%</t>
+          <t>19,06%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10330,32 +10330,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>141113</t>
+          <t>122575</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>108295</t>
+          <t>105248</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>270483</t>
+          <t>142384</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>20,75%</t>
+          <t>17,02%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>15,93%</t>
+          <t>14,61%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>39,78%</t>
+          <t>19,77%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10365,32 +10365,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>265538</t>
+          <t>278808</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>177949</t>
+          <t>249524</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>356306</t>
+          <t>315853</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>14,82%</t>
+          <t>16,44%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>9,93%</t>
+          <t>14,71%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>19,89%</t>
+          <t>18,62%</t>
         </is>
       </c>
     </row>
@@ -10408,17 +10408,17 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>1111663</t>
+          <t>975898</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>1111663</t>
+          <t>975898</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>1111663</t>
+          <t>975898</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -10443,17 +10443,17 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>679944</t>
+          <t>720378</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>679944</t>
+          <t>720378</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>679944</t>
+          <t>720378</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -10478,17 +10478,17 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>1791607</t>
+          <t>1696276</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1791607</t>
+          <t>1696276</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1791607</t>
+          <t>1696276</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
